--- a/data/8Juni-Razorbacks-v-Oaks.xlsx
+++ b/data/8Juni-Razorbacks-v-Oaks.xlsx
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O139"/>
   <sheetData>
     <row r="1">
@@ -980,8 +980,10 @@
       <c r="D115" t="s">
         <v>43</v>
       </c>
-      <c r="E115" t="s">
-        <v>44</v>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>DW</t>
+        </is>
       </c>
     </row>
     <row r="116">
